--- a/SGC-CKN/Excel/p15htd_Cọc_khoan_nhồi_-_Trụ_HN478_C4_D2000_01-03-2026.xlsx
+++ b/SGC-CKN/Excel/p15htd_Cọc_khoan_nhồi_-_Trụ_HN478_C4_D2000_01-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="74">
   <si>
     <t>Dự án</t>
   </si>
@@ -47,7 +47,7 @@
     <t>Đường kính</t>
   </si>
   <si>
-    <t>D2000</t>
+    <t>D1200</t>
   </si>
   <si>
     <t>Bắt đầu thi công</t>
@@ -95,9 +95,6 @@
     <t>1</t>
   </si>
   <si>
-    <t>Cát mịn màu xám lẫn bùn sét, mùn thực vật, kết cấu xốp</t>
-  </si>
-  <si>
     <t xml:space="preserve">10h30
 28/02/2026</t>
   </si>
@@ -154,9 +151,6 @@
     <t>3</t>
   </si>
   <si>
-    <t>Sét xám ghi, trạng thái dẻo cứng</t>
-  </si>
-  <si>
     <t xml:space="preserve">14h19
 28/02/2026</t>
   </si>
@@ -166,9 +160,6 @@
   </si>
   <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>Cát, sạn, sỏi nhỏ màu xám ghi, kết cấu chặt vừa</t>
   </si>
   <si>
     <t xml:space="preserve">15h12
@@ -279,7 +270,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -330,11 +321,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF4C1D95"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="12"/>
@@ -347,7 +333,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -397,11 +383,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFECACA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDD6FE"/>
       </patternFill>
     </fill>
     <fill>
@@ -497,7 +478,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -553,22 +534,13 @@
     <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1145,13 +1117,13 @@
         <v>11</v>
       </c>
       <c r="C11" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="E11" s="7" t="s">
         <v>28</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>29</v>
       </c>
       <c r="F11" s="5">
         <v>-9.52</v>
@@ -1169,7 +1141,7 @@
         <v>3.44</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1180,13 +1152,13 @@
         <v>11</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F12" s="5">
         <v>-10.38</v>
@@ -1204,7 +1176,7 @@
         <v>3.96</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1215,13 +1187,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D13" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>31</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>32</v>
       </c>
       <c r="F13" s="5">
         <v>-11.7</v>
@@ -1239,7 +1211,7 @@
         <v>5.01</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1250,13 +1222,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D14" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>33</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>34</v>
       </c>
       <c r="F14" s="5">
         <v>-13.62</v>
@@ -1274,7 +1246,7 @@
         <v>7.56</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1285,13 +1257,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D15" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>34</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>35</v>
       </c>
       <c r="F15" s="5">
         <v>-15.51</v>
@@ -1309,24 +1281,24 @@
         <v>3.25</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="11" t="s">
+      <c r="D16" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" s="12" t="s">
         <v>37</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>38</v>
       </c>
       <c r="F16" s="10">
         <v>-16.7</v>
@@ -1344,24 +1316,24 @@
         <v>4.17</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B17" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="11" t="s">
+      <c r="D17" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="E17" s="12" t="s">
         <v>38</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>39</v>
       </c>
       <c r="F17" s="10">
         <v>-18.3</v>
@@ -1379,24 +1351,24 @@
         <v>7.03</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>37</v>
-      </c>
       <c r="D18" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18" s="12" t="s">
         <v>39</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>40</v>
       </c>
       <c r="F18" s="10">
         <v>-20.41</v>
@@ -1414,24 +1386,24 @@
         <v>7.2</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>37</v>
-      </c>
       <c r="D19" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19" s="12" t="s">
         <v>40</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>41</v>
       </c>
       <c r="F19" s="10">
         <v>-22.33</v>
@@ -1449,24 +1421,24 @@
         <v>5.68</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E20" s="15" t="s">
         <v>42</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>44</v>
       </c>
       <c r="F20" s="13">
         <v>-24.6</v>
@@ -1484,24 +1456,24 @@
         <v>6.57</v>
       </c>
       <c r="K20" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="14" t="s">
+      <c r="E21" s="15" t="s">
         <v>43</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>45</v>
       </c>
       <c r="F21" s="13">
         <v>-26.9</v>
@@ -1519,618 +1491,618 @@
         <v>4.15</v>
       </c>
       <c r="K21" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="D22" s="18" t="s">
+      <c r="A22" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="E22" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="F22" s="16">
+      <c r="F22" s="13">
         <v>-28.7</v>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="13">
         <v>-30.64</v>
       </c>
-      <c r="H22" s="16">
+      <c r="H22" s="13">
         <v>0.45</v>
       </c>
-      <c r="I22" s="16">
+      <c r="I22" s="13">
         <v>1.94</v>
       </c>
       <c r="J22" s="8">
         <v>4.31</v>
       </c>
-      <c r="K22" s="17" t="s">
-        <v>30</v>
+      <c r="K22" s="14" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E23" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="E23" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="F23" s="16">
+      <c r="F23" s="13">
         <v>-30.64</v>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="13">
         <v>-32.68</v>
       </c>
-      <c r="H23" s="16">
+      <c r="H23" s="13">
         <v>0.4</v>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="13">
         <v>2.04</v>
       </c>
       <c r="J23" s="9">
         <v>5.1</v>
       </c>
-      <c r="K23" s="17" t="s">
-        <v>30</v>
+      <c r="K23" s="14" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="17" t="s">
+      <c r="E24" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="D24" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="E24" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="F24" s="16">
+      <c r="F24" s="13">
         <v>-32.68</v>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="13">
         <v>-34.71</v>
       </c>
-      <c r="H24" s="16">
+      <c r="H24" s="13">
         <v>0.48</v>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="13">
         <v>2.03</v>
       </c>
       <c r="J24" s="8">
         <v>4.2</v>
       </c>
-      <c r="K24" s="17" t="s">
-        <v>30</v>
+      <c r="K24" s="14" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D25" s="21" t="s">
+      <c r="A25" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="E25" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E25" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="F25" s="19">
+      <c r="F25" s="16">
         <v>-34.71</v>
       </c>
-      <c r="G25" s="19">
+      <c r="G25" s="16">
         <v>-36.82</v>
       </c>
-      <c r="H25" s="19">
+      <c r="H25" s="16">
         <v>0.4</v>
       </c>
-      <c r="I25" s="19">
+      <c r="I25" s="16">
         <v>2.11</v>
       </c>
       <c r="J25" s="9">
         <v>5.27</v>
       </c>
-      <c r="K25" s="20" t="s">
-        <v>30</v>
+      <c r="K25" s="17" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="19" t="s">
+      <c r="A26" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="E26" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="B26" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D26" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="E26" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="F26" s="19">
+      <c r="F26" s="16">
         <v>-36.82</v>
       </c>
-      <c r="G26" s="19">
+      <c r="G26" s="16">
         <v>-38.95</v>
       </c>
-      <c r="H26" s="19">
+      <c r="H26" s="16">
         <v>0.3</v>
       </c>
-      <c r="I26" s="19">
+      <c r="I26" s="16">
         <v>2.13</v>
       </c>
       <c r="J26" s="9">
         <v>7.1</v>
       </c>
-      <c r="K26" s="20" t="s">
-        <v>30</v>
+      <c r="K26" s="17" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="19" t="s">
+      <c r="A27" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D27" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="B27" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="20" t="s">
+      <c r="E27" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D27" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="E27" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="F27" s="19">
+      <c r="F27" s="16">
         <v>-38.95</v>
       </c>
-      <c r="G27" s="19">
+      <c r="G27" s="16">
         <v>-41.12</v>
       </c>
-      <c r="H27" s="19">
+      <c r="H27" s="16">
         <v>0.5</v>
       </c>
-      <c r="I27" s="19">
+      <c r="I27" s="16">
         <v>2.17</v>
       </c>
       <c r="J27" s="8">
         <v>4.34</v>
       </c>
-      <c r="K27" s="20" t="s">
-        <v>30</v>
+      <c r="K27" s="17" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="28" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="20" t="s">
+      <c r="A28" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D28" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D28" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="E28" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="F28" s="19">
+      <c r="E28" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="F28" s="16">
         <v>-41.12</v>
       </c>
-      <c r="G28" s="19">
+      <c r="G28" s="16">
         <v>-43.25</v>
       </c>
-      <c r="H28" s="19">
+      <c r="H28" s="16">
         <v>0.25</v>
       </c>
-      <c r="I28" s="19">
+      <c r="I28" s="16">
         <v>2.13</v>
       </c>
       <c r="J28" s="9">
         <v>8.52</v>
       </c>
-      <c r="K28" s="20" t="s">
-        <v>30</v>
+      <c r="K28" s="17" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="29" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B29" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D29" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="E29" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="F29" s="19">
+      <c r="A29" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="E29" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="F29" s="16">
         <v>-43.25</v>
       </c>
-      <c r="G29" s="19">
+      <c r="G29" s="16">
         <v>-45.36</v>
       </c>
-      <c r="H29" s="19">
+      <c r="H29" s="16">
         <v>0.3</v>
       </c>
-      <c r="I29" s="19">
+      <c r="I29" s="16">
         <v>2.11</v>
       </c>
       <c r="J29" s="9">
         <v>7.03</v>
       </c>
-      <c r="K29" s="20" t="s">
-        <v>30</v>
+      <c r="K29" s="17" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="30" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B30" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D30" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="E30" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="F30" s="19">
+      <c r="A30" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="F30" s="16">
         <v>-45.36</v>
       </c>
-      <c r="G30" s="19">
+      <c r="G30" s="16">
         <v>-47.17</v>
       </c>
-      <c r="H30" s="19">
+      <c r="H30" s="16">
         <v>0.57</v>
       </c>
-      <c r="I30" s="19">
+      <c r="I30" s="16">
         <v>1.81</v>
       </c>
       <c r="J30" s="8">
         <v>3.19</v>
       </c>
-      <c r="K30" s="20" t="s">
-        <v>30</v>
+      <c r="K30" s="17" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="31" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B31" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D31" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="E31" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="F31" s="19">
+      <c r="A31" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="F31" s="16">
         <v>-47.17</v>
       </c>
-      <c r="G31" s="19">
+      <c r="G31" s="16">
         <v>-49.54</v>
       </c>
-      <c r="H31" s="19">
+      <c r="H31" s="16">
         <v>0.6</v>
       </c>
-      <c r="I31" s="19">
+      <c r="I31" s="16">
         <v>2.37</v>
       </c>
       <c r="J31" s="8">
         <v>3.95</v>
       </c>
-      <c r="K31" s="20" t="s">
-        <v>30</v>
+      <c r="K31" s="17" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="32" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B32" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D32" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E32" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="F32" s="19">
+      <c r="A32" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="E32" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="F32" s="16">
         <v>-49.54</v>
       </c>
-      <c r="G32" s="19">
+      <c r="G32" s="16">
         <v>-51.68</v>
       </c>
-      <c r="H32" s="19">
+      <c r="H32" s="16">
         <v>0.95</v>
       </c>
-      <c r="I32" s="19">
+      <c r="I32" s="16">
         <v>2.14</v>
       </c>
       <c r="J32" s="8">
         <v>2.25</v>
       </c>
-      <c r="K32" s="20" t="s">
-        <v>30</v>
+      <c r="K32" s="17" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B33" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D33" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="E33" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="F33" s="19">
+      <c r="A33" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D33" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="F33" s="16">
         <v>-51.68</v>
       </c>
-      <c r="G33" s="19">
+      <c r="G33" s="16">
         <v>-53.57</v>
       </c>
-      <c r="H33" s="19">
+      <c r="H33" s="16">
         <v>0.8</v>
       </c>
-      <c r="I33" s="19">
+      <c r="I33" s="16">
         <v>1.89</v>
       </c>
       <c r="J33" s="8">
         <v>2.36</v>
       </c>
-      <c r="K33" s="20" t="s">
-        <v>30</v>
+      <c r="K33" s="17" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="34" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B34" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D34" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="E34" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="F34" s="19">
+      <c r="A34" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D34" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="E34" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F34" s="16">
         <v>-53.57</v>
       </c>
-      <c r="G34" s="19">
+      <c r="G34" s="16">
         <v>-55.32</v>
       </c>
-      <c r="H34" s="19">
+      <c r="H34" s="16">
         <v>0.58</v>
       </c>
-      <c r="I34" s="19">
+      <c r="I34" s="16">
         <v>1.75</v>
       </c>
       <c r="J34" s="8">
         <v>3</v>
       </c>
-      <c r="K34" s="20" t="s">
-        <v>30</v>
+      <c r="K34" s="17" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="35" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B35" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D35" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="E35" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="F35" s="19">
+      <c r="A35" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="E35" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="F35" s="16">
         <v>-55.32</v>
       </c>
-      <c r="G35" s="19">
+      <c r="G35" s="16">
         <v>-57.13</v>
       </c>
-      <c r="H35" s="19">
+      <c r="H35" s="16">
         <v>0.62</v>
       </c>
-      <c r="I35" s="19">
+      <c r="I35" s="16">
         <v>1.81</v>
       </c>
       <c r="J35" s="8">
         <v>2.94</v>
       </c>
-      <c r="K35" s="20" t="s">
-        <v>30</v>
+      <c r="K35" s="17" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="36" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B36" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D36" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="E36" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="F36" s="19">
+      <c r="A36" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D36" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="E36" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="F36" s="16">
         <v>-57.13</v>
       </c>
-      <c r="G36" s="19">
+      <c r="G36" s="16">
         <v>-59.27</v>
       </c>
-      <c r="H36" s="19">
+      <c r="H36" s="16">
         <v>0.63</v>
       </c>
-      <c r="I36" s="19">
+      <c r="I36" s="16">
         <v>2.14</v>
       </c>
       <c r="J36" s="8">
         <v>3.38</v>
       </c>
-      <c r="K36" s="20" t="s">
-        <v>30</v>
+      <c r="K36" s="17" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B37" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C37" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D37" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="E37" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="F37" s="19">
+      <c r="A37" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D37" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E37" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F37" s="16">
         <v>-59.27</v>
       </c>
-      <c r="G37" s="19">
+      <c r="G37" s="16">
         <v>-61.05</v>
       </c>
-      <c r="H37" s="19">
+      <c r="H37" s="16">
         <v>0.75</v>
       </c>
-      <c r="I37" s="19">
+      <c r="I37" s="16">
         <v>1.78</v>
       </c>
       <c r="J37" s="8">
         <v>2.37</v>
       </c>
-      <c r="K37" s="20" t="s">
-        <v>30</v>
+      <c r="K37" s="17" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="38" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B38" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C38" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D38" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E38" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="F38" s="19">
+      <c r="A38" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D38" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="E38" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="F38" s="16">
         <v>-61.05</v>
       </c>
-      <c r="G38" s="19">
+      <c r="G38" s="16">
         <v>-63.05</v>
       </c>
-      <c r="H38" s="19">
+      <c r="H38" s="16">
         <v>1.42</v>
       </c>
-      <c r="I38" s="19">
+      <c r="I38" s="16">
         <v>2</v>
       </c>
       <c r="J38" s="8">
         <v>1.41</v>
       </c>
-      <c r="K38" s="20" t="s">
-        <v>30</v>
+      <c r="K38" s="17" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="41" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="B41" s="22"/>
-      <c r="C41" s="22"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="22"/>
-      <c r="I41" s="22"/>
-      <c r="J41" s="22"/>
-      <c r="K41" s="22"/>
+      <c r="A41" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="B41" s="19"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="19"/>
+      <c r="I41" s="19"/>
+      <c r="J41" s="19"/>
+      <c r="K41" s="19"/>
     </row>
     <row r="42" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="43" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2212,7 +2184,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -2225,31 +2197,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2260,7 +2232,7 @@
         <v>11</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D2" s="5">
         <v>5</v>
@@ -2289,7 +2261,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D3" s="10">
         <v>4</v>
@@ -2318,25 +2290,25 @@
         <v>11</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="D4" s="13">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E4" s="13">
         <v>-24.6</v>
       </c>
       <c r="F4" s="13">
-        <v>-28.7</v>
+        <v>-34.71</v>
       </c>
       <c r="G4" s="13">
-        <v>0.78</v>
+        <v>2.12</v>
       </c>
       <c r="H4" s="13">
-        <v>4.1</v>
-      </c>
-      <c r="I4" s="9">
-        <v>5.23</v>
+        <v>10.11</v>
+      </c>
+      <c r="I4" s="8">
+        <v>4.78</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2347,82 +2319,53 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D5" s="16">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E5" s="16">
-        <v>-28.7</v>
+        <v>-34.71</v>
       </c>
       <c r="F5" s="16">
-        <v>-34.71</v>
+        <v>-63.05</v>
       </c>
       <c r="G5" s="16">
-        <v>1.33</v>
+        <v>8.67</v>
       </c>
       <c r="H5" s="16">
-        <v>6.01</v>
+        <v>28.34</v>
       </c>
       <c r="I5" s="8">
-        <v>4.51</v>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="19">
-        <v>5</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="19">
-        <v>14</v>
-      </c>
-      <c r="E6" s="19">
-        <v>-34.71</v>
-      </c>
-      <c r="F6" s="19">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="21">
+        <v>28</v>
+      </c>
+      <c r="E6" s="21">
+        <v>-9.52</v>
+      </c>
+      <c r="F6" s="21">
         <v>-63.05</v>
       </c>
-      <c r="G6" s="19">
-        <v>8.67</v>
-      </c>
-      <c r="H6" s="19">
-        <v>28.34</v>
-      </c>
-      <c r="I6" s="8">
-        <v>3.27</v>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="24">
-        <v>28</v>
-      </c>
-      <c r="E7" s="24">
-        <v>-9.52</v>
-      </c>
-      <c r="F7" s="24">
-        <v>-63.05</v>
-      </c>
-      <c r="G7" s="24">
+      <c r="G6" s="21">
         <v>13.72</v>
       </c>
-      <c r="H7" s="24">
+      <c r="H6" s="21">
         <v>53.53</v>
       </c>
-      <c r="I7" s="24">
+      <c r="I6" s="21">
         <v>3.9</v>
       </c>
     </row>
